--- a/data/output/stats-fray-winter_2026.xlsx
+++ b/data/output/stats-fray-winter_2026.xlsx
@@ -3464,12 +3464,12 @@
           <t>Team OPS</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Through Date</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Workbook Season</t>
         </is>

--- a/data/output/stats-fray-winter_2026.xlsx
+++ b/data/output/stats-fray-winter_2026.xlsx
@@ -12,26 +12,26 @@
     <sheet name="Player Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Cyclo Total" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Cyclo Winter 2026 Total" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cyclo Winter 2026 Game 1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Cyclo Winter 2026 Game 2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cyclo Winter 2026 Game 3" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Cyclo Winter 2026 Game 7" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cyclo Winter 2026 Game 6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cyclo Winter 2026 Game 5" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Cyclo Winter 2026 Game 4" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Cyclo Winter 2026 Game 5" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Cyclo Winter 2026 Game 6" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Cyclo Winter 2026 Game 7" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Cyclo Winter 2026 Game 3" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Cyclo Winter 2026 Game 2" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Cyclo Winter 2026 Game 1" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'League Summary'!$A$1:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Player Summary'!$A$1:$Q$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cyclo Total'!$A$1:$Q$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cyclo Winter 2026 Total'!$A$1:$Q$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cyclo Winter 2026 Game 1'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cyclo Winter 2026 Game 2'!$A$1:$Q$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Cyclo Winter 2026 Game 3'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cyclo Winter 2026 Game 7'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cyclo Winter 2026 Game 6'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Cyclo Winter 2026 Game 5'!$A$1:$Q$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Cyclo Winter 2026 Game 4'!$A$1:$Q$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cyclo Winter 2026 Game 5'!$A$1:$Q$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Cyclo Winter 2026 Game 6'!$A$1:$Q$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Cyclo Winter 2026 Game 7'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cyclo Winter 2026 Game 3'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Cyclo Winter 2026 Game 2'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Cyclo Winter 2026 Game 1'!$A$1:$Q$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -938,35 +938,35 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.250</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -987,55 +987,55 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>0.500</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.750</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1047,49 +1047,49 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>2.333</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>3.333</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1110,58 +1110,58 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.667</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1173,52 +1173,52 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.400</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1233,39 +1233,39 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Kunal</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1275,10 +1275,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1299,36 +1299,36 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1338,13 +1338,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1362,58 +1362,58 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rich</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1425,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1442,19 +1442,19 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Ramos</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1464,10 +1464,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1491,94 +1491,157 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>0.333</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>0.333</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>0.333</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>0.666</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0.607</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0.607</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0.964</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1.571</t>
+      <c r="B14" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0.833</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1.333</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q11"/>
+  <autoFilter ref="A1:Q12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1706,19 +1769,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1736,29 +1799,29 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -1769,19 +1832,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1790,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -1799,10 +1862,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1841,13 +1904,13 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1862,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
@@ -1879,12 +1942,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>2.000</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>3.000</t>
         </is>
       </c>
     </row>
@@ -1898,16 +1961,16 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1916,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1925,29 +1988,29 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
@@ -1961,16 +2024,16 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1979,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1995,22 +2058,22 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.667</t>
         </is>
       </c>
     </row>
@@ -2027,10 +2090,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2051,29 +2114,29 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -2093,16 +2156,16 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2114,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
@@ -2131,12 +2194,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>4.000</t>
         </is>
       </c>
     </row>
@@ -2147,19 +2210,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2184,22 +2247,22 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -2213,13 +2276,13 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -2231,7 +2294,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -2240,29 +2303,29 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -2273,10 +2336,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
@@ -2285,13 +2348,13 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -2303,52 +2366,52 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2357,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -2366,49 +2429,49 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2417,10 +2480,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2429,29 +2492,29 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>2.000</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -2462,28 +2525,28 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F15" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="G15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0</v>
@@ -2492,29 +2555,29 @@
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1.348</t>
+          <t>1.375</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>2.044</t>
+          <t>2.250</t>
         </is>
       </c>
     </row>
@@ -2653,10 +2716,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -2677,29 +2740,29 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>2.333</t>
         </is>
       </c>
     </row>
@@ -2713,25 +2776,25 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2740,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>2</v>
@@ -2757,12 +2820,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>5.000</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2839,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -2797,35 +2860,35 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>0.333</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.333</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
@@ -2908,13 +2971,13 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2929,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -2946,12 +3009,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.250</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -2968,13 +3031,13 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2992,29 +3055,29 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3091,7 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -3058,55 +3121,55 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3118,40 +3181,40 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.666</t>
+          <t>1.750</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -3160,19 +3223,19 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3181,10 +3244,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3193,43 +3256,43 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Ramos</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -3244,52 +3307,52 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -3310,26 +3373,26 @@
         <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -3349,31 +3412,31 @@
         <v>19</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -3387,12 +3450,12 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>0.848</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.424</t>
         </is>
       </c>
     </row>
@@ -7362,10 +7425,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -7386,29 +7449,29 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.333</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.333</t>
+          <t>1.667</t>
         </is>
       </c>
     </row>
@@ -7422,25 +7485,25 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -7449,7 +7512,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>2</v>
@@ -7466,12 +7529,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>5.000</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7548,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -7506,20 +7569,20 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -7529,12 +7592,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1.333</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7638,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
@@ -7617,13 +7680,13 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -7638,7 +7701,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -7655,12 +7718,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -7677,13 +7740,13 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -7701,29 +7764,29 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7800,7 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -7767,55 +7830,55 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -7827,40 +7890,40 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.750</t>
+          <t>1.666</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Ramos</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -7869,19 +7932,19 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -7890,10 +7953,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -7902,43 +7965,43 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -7953,52 +8016,52 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8019,26 +8082,26 @@
         <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.250</t>
         </is>
       </c>
     </row>
@@ -8058,31 +8121,31 @@
         <v>19</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -8096,12 +8159,12 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>1.061</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>1.424</t>
+          <t>1.637</t>
         </is>
       </c>
     </row>
@@ -8234,19 +8297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -8264,29 +8327,29 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -8297,19 +8360,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -8318,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -8327,10 +8390,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -8369,13 +8432,13 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -8390,7 +8453,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
@@ -8407,12 +8470,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
@@ -8426,16 +8489,16 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -8444,7 +8507,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -8453,29 +8516,29 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>3.000</t>
         </is>
       </c>
     </row>
@@ -8489,16 +8552,16 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -8507,7 +8570,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -8523,12 +8586,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -8538,7 +8601,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -8555,10 +8618,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -8579,29 +8642,29 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
@@ -8621,16 +8684,16 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -8642,7 +8705,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
@@ -8659,12 +8722,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>3.500</t>
         </is>
       </c>
     </row>
@@ -8675,19 +8738,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -8712,22 +8775,22 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -8741,13 +8804,13 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -8759,7 +8822,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -8768,29 +8831,29 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
@@ -8801,10 +8864,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
@@ -8813,13 +8876,13 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -8831,52 +8894,52 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>4.000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Ramos</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8885,7 +8948,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -8894,49 +8957,49 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>0.667</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -8945,10 +9008,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -8957,29 +9020,29 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -8990,28 +9053,28 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0</v>
@@ -9020,29 +9083,29 @@
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.696</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0.696</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.348</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>2.044</t>
         </is>
       </c>
     </row>
@@ -9059,7 +9122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9175,19 +9238,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -9208,7 +9271,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9222,35 +9285,35 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -9271,16 +9334,16 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -9290,36 +9353,36 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9331,49 +9394,49 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2.333</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>3.333</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -9382,7 +9445,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9394,58 +9457,58 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.667</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9457,52 +9520,52 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.400</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -9517,39 +9580,39 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -9559,10 +9622,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -9583,36 +9646,36 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -9622,13 +9685,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -9646,58 +9709,58 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.667</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Rich</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -9709,10 +9772,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9726,19 +9789,19 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -9748,10 +9811,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -9775,157 +9838,94 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.334</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
           <t>0.666</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0.833</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1.333</t>
+      <c r="B13" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0.607</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.607</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0.964</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1.571</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q12"/>
+  <autoFilter ref="A1:Q11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
